--- a/data/adicionales.xlsx
+++ b/data/adicionales.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/05 Mayo/Dasboatdde abril/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/06 Junio/Dasboatdde mayo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{12694562-3CF4-40B0-8A8E-F17B899F2747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCF5664-CF0D-44DD-8D67-182376D76EBD}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{12694562-3CF4-40B0-8A8E-F17B899F2747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04F749A6-155A-4D31-B7B6-ED0EB781E0C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E44F7BE-EA21-4B2C-8EEA-8FB69F4EDA70}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
   <si>
     <t>Sucursal</t>
   </si>
@@ -143,27 +143,15 @@
     <t>Motorola Edge 60 Fusion 256gb</t>
   </si>
   <si>
-    <t>Honor X8c 512gb</t>
-  </si>
-  <si>
     <t>Oppo A5 256gb</t>
   </si>
   <si>
     <t>Oppo A5 256gb 4g</t>
   </si>
   <si>
-    <t>Zte Blade A76 128gb 5g</t>
-  </si>
-  <si>
     <t>Motorola Moto G56 256gb</t>
   </si>
   <si>
-    <t>Motorola Moto G05 256gb</t>
-  </si>
-  <si>
-    <t>Honor Magic 8 Lite 512Gb</t>
-  </si>
-  <si>
     <t>Honor X8D 512Gb</t>
   </si>
   <si>
@@ -179,15 +167,6 @@
     <t>CargoBasico</t>
   </si>
   <si>
-    <t>Conectados 26.1 V 53.9_lo</t>
-  </si>
-  <si>
-    <t>Conectados 26.1 V 44.9</t>
-  </si>
-  <si>
-    <t>Conectados 26.1 V 53.9_cn</t>
-  </si>
-  <si>
     <t>Conectados V 3.1 Mx</t>
   </si>
   <si>
@@ -200,81 +179,6 @@
     <t>Top 10 planes mas vendido</t>
   </si>
   <si>
-    <t>Oficina principal</t>
-  </si>
-  <si>
-    <t>Caldas</t>
-  </si>
-  <si>
-    <t>Don Matias</t>
-  </si>
-  <si>
-    <t>Sabaneta</t>
-  </si>
-  <si>
-    <t>Junín</t>
-  </si>
-  <si>
-    <t>Itagui</t>
-  </si>
-  <si>
-    <t>Barbosa</t>
-  </si>
-  <si>
-    <t>Copacabana</t>
-  </si>
-  <si>
-    <t>El Bagre</t>
-  </si>
-  <si>
-    <t>Girardota</t>
-  </si>
-  <si>
-    <t>Segovia</t>
-  </si>
-  <si>
-    <t>Envigado</t>
-  </si>
-  <si>
-    <t>Zaragoza</t>
-  </si>
-  <si>
-    <t>Bello</t>
-  </si>
-  <si>
-    <t>Frontino</t>
-  </si>
-  <si>
-    <t>Yarumal</t>
-  </si>
-  <si>
-    <t>Prado</t>
-  </si>
-  <si>
-    <t>Ciudad Bolivar</t>
-  </si>
-  <si>
-    <t>Caucasia</t>
-  </si>
-  <si>
-    <t>Dabeiba</t>
-  </si>
-  <si>
-    <t>Nechi</t>
-  </si>
-  <si>
-    <t>La Estrella</t>
-  </si>
-  <si>
-    <t>Junin</t>
-  </si>
-  <si>
-    <t>Terminal Norte</t>
-  </si>
-  <si>
-    <t>Numerario</t>
-  </si>
-  <si>
     <t>Samsung Galaxy A17 256gb</t>
   </si>
   <si>
@@ -293,19 +197,42 @@
     <t>Conectados 26.1 V 56.9_ap1</t>
   </si>
   <si>
-    <t>Terminal del norte</t>
-  </si>
-  <si>
     <t>SAN CRISTOBAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN CRISTOBAL </t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>Conectados 26.1v99.9lo_ts_ap1l</t>
+  </si>
+  <si>
+    <t>Conectados 26.1v99.9lo_tm_ap1l</t>
+  </si>
+  <si>
+    <t>Conectados 26.1 V75.9lo_mm_ap1</t>
+  </si>
+  <si>
+    <t>Paquete Power 26.1 V 47.9</t>
+  </si>
+  <si>
+    <t>Motorola Moto G77 256Gb 5G</t>
+  </si>
+  <si>
+    <t>Xiaomi Redmi 15c 256gb</t>
+  </si>
+  <si>
+    <t>Honor X7d 256gb</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -359,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -385,12 +312,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -400,7 +342,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -408,10 +349,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -758,7 +704,7 @@
     <col min="7" max="7" width="16.42578125" customWidth="1"/>
     <col min="10" max="10" width="28.5703125" customWidth="1"/>
     <col min="12" max="12" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -770,508 +716,418 @@
         <v>32</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="6"/>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="14">
+        <v>146</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="14">
+        <v>53900</v>
+      </c>
+      <c r="P3" s="14">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="6"/>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="5">
+        <v>19</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="14">
+        <v>132</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="14">
+        <v>46900</v>
+      </c>
+      <c r="P4" s="14">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="6"/>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5">
+        <v>19</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="14">
+        <v>107</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="14">
+        <v>51900</v>
+      </c>
+      <c r="P5" s="14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="6"/>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="5">
+        <v>7</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="14">
+        <v>90</v>
+      </c>
+      <c r="N6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="O6" s="14">
+        <v>53900</v>
+      </c>
+      <c r="P6" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="6"/>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5">
+        <v>18</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="14">
+        <v>88</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" s="14">
+        <v>66700</v>
+      </c>
+      <c r="P7" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="6"/>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5">
+        <v>5</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="14">
+        <v>88</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="14">
+        <v>66700</v>
+      </c>
+      <c r="P8" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="6"/>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="14">
+        <v>73</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" s="14">
+        <v>51600</v>
+      </c>
+      <c r="P9" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="6"/>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="14">
+        <v>67</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" s="14">
+        <v>61600</v>
+      </c>
+      <c r="P10" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="6"/>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="5">
+        <v>12</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="14">
+        <v>64</v>
+      </c>
+      <c r="N11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="O11" s="14">
+        <v>38900</v>
+      </c>
+      <c r="P11" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="6"/>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="14">
+        <v>58</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="14">
+        <v>47900</v>
+      </c>
+      <c r="P12" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="6"/>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="5">
+        <v>7</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="N13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13" s="14">
+        <v>44900</v>
+      </c>
+      <c r="P13" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="6"/>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="6"/>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="6"/>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="6"/>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="6"/>
+      <c r="F18" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="7">
-        <v>88</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G18" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="6"/>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="6"/>
+      <c r="F20" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="6">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3">
-        <v>109</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O3" s="11">
-        <v>53900</v>
-      </c>
-      <c r="P3">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="7">
-        <v>55</v>
-      </c>
-      <c r="F4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="6">
-        <v>22</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4">
-        <v>108</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="O4" s="11">
-        <v>46900</v>
-      </c>
-      <c r="P4">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="7">
-        <v>54</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="6">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5">
-        <v>96</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="11">
-        <v>44900</v>
-      </c>
-      <c r="P5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="7">
-        <v>49</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="6">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6">
-        <v>88</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="O6" s="11">
-        <v>50900</v>
-      </c>
-      <c r="P6">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="7">
-        <v>49</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="6">
-        <v>13</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7">
-        <v>73</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" s="11">
-        <v>38900</v>
-      </c>
-      <c r="P7">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="7">
-        <v>49</v>
-      </c>
-      <c r="F8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="6">
-        <v>11</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K8">
-        <v>64</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O8" s="11">
-        <v>51600</v>
-      </c>
-      <c r="P8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="7">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="6">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>60</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="O9" s="11">
-        <v>44900</v>
-      </c>
-      <c r="P9">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="7">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="6">
-        <v>10</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="O10" s="11">
-        <v>51900</v>
-      </c>
-      <c r="P10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="7">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="6">
-        <v>9</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11">
-        <v>45</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O11" s="11">
-        <v>51600</v>
-      </c>
-      <c r="P11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="6"/>
+      <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="6"/>
+      <c r="F22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" s="6">
-        <v>6</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12">
-        <v>45</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O12" s="11">
-        <v>53900</v>
-      </c>
-      <c r="P12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="7">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="6">
-        <v>4</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="7">
-        <v>20</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="7">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="7">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="7">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="7">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="7">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="7">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="7">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="7">
-        <v>7</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="6"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="10">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="12">
-        <v>646</v>
-      </c>
+      <c r="B26" s="10"/>
     </row>
     <row r="30" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
@@ -1279,25 +1135,25 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1849,7 +1705,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2">
         <v>0</v>

--- a/data/adicionales.xlsx
+++ b/data/adicionales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/06 Junio/Dasboatdde mayo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/07 Julio/Dasboatdde junio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{12694562-3CF4-40B0-8A8E-F17B899F2747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04F749A6-155A-4D31-B7B6-ED0EB781E0C9}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{12694562-3CF4-40B0-8A8E-F17B899F2747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC671FCF-FCA0-4830-A0E8-72B05871A065}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E44F7BE-EA21-4B2C-8EEA-8FB69F4EDA70}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t>Sucursal</t>
   </si>
@@ -110,12 +110,6 @@
     <t>GIRARDOTA</t>
   </si>
   <si>
-    <t>TERMINAL DEL NORTE</t>
-  </si>
-  <si>
-    <t>NECHI</t>
-  </si>
-  <si>
     <t>YARUMAL</t>
   </si>
   <si>
@@ -149,9 +143,6 @@
     <t>Oppo A5 256gb 4g</t>
   </si>
   <si>
-    <t>Motorola Moto G56 256gb</t>
-  </si>
-  <si>
     <t>Honor X8D 512Gb</t>
   </si>
   <si>
@@ -167,9 +158,6 @@
     <t>CargoBasico</t>
   </si>
   <si>
-    <t>Conectados V 3.1 Mx</t>
-  </si>
-  <si>
     <t>Paquete Power 26.1 V 53.9</t>
   </si>
   <si>
@@ -191,9 +179,6 @@
     <t>Conectados 26. 1 E 46.9</t>
   </si>
   <si>
-    <t>Conectados 26.1 E 49.9_ap1</t>
-  </si>
-  <si>
     <t>Conectados 26.1 V 56.9_ap1</t>
   </si>
   <si>
@@ -206,33 +191,46 @@
     <t>TERMINAL NORTE</t>
   </si>
   <si>
-    <t>Conectados 26.1v99.9lo_ts_ap1l</t>
-  </si>
-  <si>
-    <t>Conectados 26.1v99.9lo_tm_ap1l</t>
-  </si>
-  <si>
-    <t>Conectados 26.1 V75.9lo_mm_ap1</t>
-  </si>
-  <si>
-    <t>Paquete Power 26.1 V 47.9</t>
-  </si>
-  <si>
     <t>Motorola Moto G77 256Gb 5G</t>
   </si>
   <si>
-    <t>Xiaomi Redmi 15c 256gb</t>
-  </si>
-  <si>
     <t>Honor X7d 256gb</t>
+  </si>
+  <si>
+    <t>Zte Blade A76 128gb 5g</t>
+  </si>
+  <si>
+    <t>Vivo Y21d  256/4gb 4g</t>
+  </si>
+  <si>
+    <t>Conectados 26.1 V65.9lo_mm_ap1</t>
+  </si>
+  <si>
+    <t>Conectados 26 E 3.3</t>
+  </si>
+  <si>
+    <t>Conectados 26.1 V65.9lo_ts_ap1</t>
+  </si>
+  <si>
+    <t>Edge Neg 60gb</t>
+  </si>
+  <si>
+    <t>Mega Protect 2 Neg2 65gb</t>
+  </si>
+  <si>
+    <t>TERMINAL</t>
+  </si>
+  <si>
+    <t>NECHÍ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -332,7 +330,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -353,12 +351,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,16 +709,16 @@
   <sheetData>
     <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="J1" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -727,128 +726,128 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>42</v>
-      </c>
       <c r="P2" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="6"/>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="5">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K3" s="14">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="14">
+        <v>45</v>
+      </c>
+      <c r="O3" s="16">
         <v>53900</v>
       </c>
       <c r="P3" s="14">
-        <v>540</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="6"/>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K4" s="14">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="14">
+        <v>46</v>
+      </c>
+      <c r="O4" s="16">
         <v>46900</v>
       </c>
       <c r="P4" s="14">
-        <v>317</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="6"/>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G5" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K5" s="14">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="14">
-        <v>51900</v>
+        <v>40</v>
+      </c>
+      <c r="O5" s="16">
+        <v>53900</v>
       </c>
       <c r="P5" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="6"/>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G6" s="5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K6" s="14">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="O6" s="14">
-        <v>53900</v>
+        <v>47</v>
+      </c>
+      <c r="O6" s="16">
+        <v>51900</v>
       </c>
       <c r="P6" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -858,19 +857,19 @@
         <v>7</v>
       </c>
       <c r="G7" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K7" s="14">
         <v>88</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="O7" s="14">
-        <v>66700</v>
+        <v>55</v>
+      </c>
+      <c r="O7" s="16">
+        <v>51600</v>
       </c>
       <c r="P7" s="14">
         <v>6</v>
@@ -880,72 +879,72 @@
       <c r="A8" s="1"/>
       <c r="B8" s="6"/>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K8" s="14">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="14">
-        <v>66700</v>
+        <v>41</v>
+      </c>
+      <c r="O8" s="16">
+        <v>51600</v>
       </c>
       <c r="P8" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="6"/>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G9" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K9" s="14">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" s="14">
-        <v>51600</v>
+        <v>56</v>
+      </c>
+      <c r="O9" s="16">
+        <v>33000</v>
       </c>
       <c r="P9" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="6"/>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G10" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K10" s="14">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="O10" s="14">
-        <v>61600</v>
+        <v>57</v>
+      </c>
+      <c r="O10" s="16">
+        <v>51600</v>
       </c>
       <c r="P10" s="14">
         <v>3</v>
@@ -955,137 +954,128 @@
       <c r="A11" s="1"/>
       <c r="B11" s="6"/>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="G11" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K11" s="14">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" s="14">
-        <v>38900</v>
+        <v>58</v>
+      </c>
+      <c r="O11" s="16">
+        <v>36330</v>
       </c>
       <c r="P11" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="6"/>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K12" s="14">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="14">
-        <v>47900</v>
+      <c r="O12" s="16">
+        <v>44900</v>
       </c>
       <c r="P12" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="6"/>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G13" s="5">
         <v>7</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="N13" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="O13" s="14">
-        <v>44900</v>
-      </c>
-      <c r="P13" s="14">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="6"/>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="5">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="6"/>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G15" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="6"/>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G16" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="6"/>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G17" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="6"/>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G18" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="6"/>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G19" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="6"/>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G20" s="5">
         <v>1</v>
@@ -1095,20 +1085,20 @@
       <c r="A21" s="1"/>
       <c r="B21" s="6"/>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="6"/>
       <c r="F22" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G22" s="9">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1125,13 +1115,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B26" s="10"/>
     </row>
     <row r="30" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1162,22 +1152,22 @@
         <v>7</v>
       </c>
       <c r="B32" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" s="2">
-        <v>1077</v>
+        <v>1301</v>
       </c>
       <c r="D32" s="2">
-        <v>4705</v>
+        <v>4336</v>
       </c>
       <c r="E32" s="2">
-        <v>571</v>
+        <v>404</v>
       </c>
       <c r="F32" s="2">
-        <v>5276</v>
+        <v>4740</v>
       </c>
       <c r="G32" s="2">
-        <v>6408</v>
+        <v>6097</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -1188,22 +1178,22 @@
         <v>8</v>
       </c>
       <c r="B33" s="2">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2">
-        <v>1520</v>
+        <v>1908</v>
       </c>
       <c r="D33" s="2">
-        <v>5390</v>
+        <v>4872</v>
       </c>
       <c r="E33" s="2">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="F33" s="2">
-        <v>6293</v>
+        <v>5760</v>
       </c>
       <c r="G33" s="2">
-        <v>7852</v>
+        <v>7715</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -1214,22 +1204,22 @@
         <v>9</v>
       </c>
       <c r="B34" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C34" s="2">
-        <v>2434</v>
+        <v>3381</v>
       </c>
       <c r="D34" s="2">
-        <v>7081</v>
+        <v>6137</v>
       </c>
       <c r="E34" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="F34" s="2">
-        <v>7474</v>
+        <v>6505</v>
       </c>
       <c r="G34" s="2">
-        <v>9936</v>
+        <v>9915</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -1240,22 +1230,22 @@
         <v>10</v>
       </c>
       <c r="B35" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2">
-        <v>1683</v>
+        <v>1527</v>
       </c>
       <c r="D35" s="2">
-        <v>3865</v>
+        <v>4168</v>
       </c>
       <c r="E35" s="2">
-        <v>524</v>
+        <v>408</v>
       </c>
       <c r="F35" s="2">
-        <v>4389</v>
+        <v>4576</v>
       </c>
       <c r="G35" s="2">
-        <v>6089</v>
+        <v>6124</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1266,22 +1256,22 @@
         <v>11</v>
       </c>
       <c r="B36" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36" s="2">
-        <v>580</v>
+        <v>795</v>
       </c>
       <c r="D36" s="2">
-        <v>1697</v>
+        <v>1482</v>
       </c>
       <c r="E36" s="2">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="F36" s="2">
-        <v>1935</v>
+        <v>1693</v>
       </c>
       <c r="G36" s="2">
-        <v>2523</v>
+        <v>2497</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -1292,22 +1282,22 @@
         <v>12</v>
       </c>
       <c r="B37" s="2">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C37" s="2">
-        <v>1429</v>
+        <v>1675</v>
       </c>
       <c r="D37" s="2">
-        <v>290</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2">
-        <v>732</v>
+        <v>634</v>
       </c>
       <c r="F37" s="2">
-        <v>1022</v>
+        <v>635</v>
       </c>
       <c r="G37" s="2">
-        <v>2586</v>
+        <v>2462</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -1318,22 +1308,22 @@
         <v>13</v>
       </c>
       <c r="B38" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2">
-        <v>1540</v>
+        <v>1398</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>410</v>
+        <v>331</v>
       </c>
       <c r="F38" s="2">
-        <v>410</v>
+        <v>331</v>
       </c>
       <c r="G38" s="2">
-        <v>2022</v>
+        <v>1798</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -1344,22 +1334,22 @@
         <v>14</v>
       </c>
       <c r="B39" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C39" s="2">
-        <v>3248</v>
+        <v>3567</v>
       </c>
       <c r="D39" s="2">
-        <v>3693</v>
+        <v>3466</v>
       </c>
       <c r="E39" s="2">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="F39" s="2">
-        <v>4021</v>
+        <v>3772</v>
       </c>
       <c r="G39" s="2">
-        <v>7280</v>
+        <v>7354</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -1370,22 +1360,22 @@
         <v>15</v>
       </c>
       <c r="B40" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C40" s="2">
-        <v>875</v>
+        <v>550</v>
       </c>
       <c r="D40" s="2">
-        <v>2340</v>
+        <v>2575</v>
       </c>
       <c r="E40" s="2">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="F40" s="2">
-        <v>2509</v>
+        <v>2678</v>
       </c>
       <c r="G40" s="2">
-        <v>3408</v>
+        <v>3253</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -1396,22 +1386,22 @@
         <v>16</v>
       </c>
       <c r="B41" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
-        <v>3937</v>
+        <v>3662</v>
       </c>
       <c r="D41" s="2">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="E41" s="2">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="F41" s="2">
-        <v>718</v>
+        <v>795</v>
       </c>
       <c r="G41" s="2">
-        <v>4731</v>
+        <v>4529</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -1422,22 +1412,22 @@
         <v>17</v>
       </c>
       <c r="B42" s="2">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
-        <v>2923</v>
+        <v>2866</v>
       </c>
       <c r="D42" s="2">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="E42" s="2">
-        <v>658</v>
+        <v>619</v>
       </c>
       <c r="F42" s="2">
-        <v>757</v>
+        <v>642</v>
       </c>
       <c r="G42" s="2">
-        <v>3797</v>
+        <v>3610</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -1451,19 +1441,19 @@
         <v>80</v>
       </c>
       <c r="C43" s="2">
-        <v>2154</v>
+        <v>2094</v>
       </c>
       <c r="D43" s="2">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2">
-        <v>952</v>
+        <v>715</v>
       </c>
       <c r="F43" s="2">
-        <v>999</v>
+        <v>777</v>
       </c>
       <c r="G43" s="2">
-        <v>3233</v>
+        <v>2951</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -1474,22 +1464,22 @@
         <v>19</v>
       </c>
       <c r="B44" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C44" s="2">
-        <v>1865</v>
+        <v>1974</v>
       </c>
       <c r="D44" s="2">
-        <v>1622</v>
+        <v>1398</v>
       </c>
       <c r="E44" s="2">
-        <v>899</v>
+        <v>1052</v>
       </c>
       <c r="F44" s="2">
-        <v>2521</v>
+        <v>2450</v>
       </c>
       <c r="G44" s="2">
-        <v>4487</v>
+        <v>4517</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -1500,22 +1490,22 @@
         <v>20</v>
       </c>
       <c r="B45" s="2">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C45" s="2">
-        <v>2841</v>
+        <v>4729</v>
       </c>
       <c r="D45" s="2">
-        <v>6609</v>
+        <v>5242</v>
       </c>
       <c r="E45" s="2">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="F45" s="2">
-        <v>7091</v>
+        <v>5651</v>
       </c>
       <c r="G45" s="2">
-        <v>9971</v>
+        <v>10406</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -1526,22 +1516,22 @@
         <v>21</v>
       </c>
       <c r="B46" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C46" s="2">
-        <v>765</v>
+        <v>657</v>
       </c>
       <c r="D46" s="2">
-        <v>1551</v>
+        <v>1630</v>
       </c>
       <c r="E46" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F46" s="2">
-        <v>1769</v>
+        <v>1860</v>
       </c>
       <c r="G46" s="2">
-        <v>2554</v>
+        <v>2540</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -1552,22 +1542,22 @@
         <v>22</v>
       </c>
       <c r="B47" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C47" s="2">
-        <v>2213</v>
+        <v>2103</v>
       </c>
       <c r="D47" s="2">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="E47" s="2">
-        <v>976</v>
+        <v>607</v>
       </c>
       <c r="F47" s="2">
-        <v>1274</v>
+        <v>942</v>
       </c>
       <c r="G47" s="2">
-        <v>3530</v>
+        <v>3090</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -1578,22 +1568,22 @@
         <v>23</v>
       </c>
       <c r="B48" s="2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C48" s="2">
-        <v>1896</v>
+        <v>2115</v>
       </c>
       <c r="D48" s="2">
-        <v>1801</v>
+        <v>1589</v>
       </c>
       <c r="E48" s="2">
-        <v>1046</v>
+        <v>913</v>
       </c>
       <c r="F48" s="2">
-        <v>2847</v>
+        <v>2502</v>
       </c>
       <c r="G48" s="2">
-        <v>4785</v>
+        <v>4677</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -1601,25 +1591,25 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B49" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="2">
-        <v>2094</v>
+        <v>2082</v>
       </c>
       <c r="D49" s="2">
-        <v>903</v>
+        <v>800</v>
       </c>
       <c r="E49" s="2">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="F49" s="2">
-        <v>1102</v>
+        <v>965</v>
       </c>
       <c r="G49" s="2">
-        <v>3204</v>
+        <v>3054</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -1627,25 +1617,25 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B50" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C50" s="2">
-        <v>1180</v>
+        <v>1273</v>
       </c>
       <c r="D50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="F50" s="2">
-        <v>281</v>
+        <v>160</v>
       </c>
       <c r="G50" s="2">
-        <v>1499</v>
+        <v>1481</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -1653,25 +1643,25 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B51" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C51" s="2">
-        <v>1481</v>
+        <v>1945</v>
       </c>
       <c r="D51" s="2">
-        <v>2026</v>
+        <v>1442</v>
       </c>
       <c r="E51" s="2">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="F51" s="2">
-        <v>2461</v>
+        <v>1915</v>
       </c>
       <c r="G51" s="2">
-        <v>3961</v>
+        <v>3870</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -1679,25 +1669,25 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B52" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C52" s="2">
-        <v>637</v>
+        <v>560</v>
       </c>
       <c r="D52" s="2">
-        <v>956</v>
+        <v>1088</v>
       </c>
       <c r="E52" s="2">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="F52" s="2">
-        <v>1105</v>
+        <v>1280</v>
       </c>
       <c r="G52" s="2">
-        <v>1749</v>
+        <v>1845</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -1705,25 +1695,25 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B53" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2">
-        <v>281</v>
+        <v>1338</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G53" s="2">
-        <v>281</v>
+        <v>1345</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -1731,25 +1721,25 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B54" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C54" s="2">
-        <v>2613</v>
+        <v>3331</v>
       </c>
       <c r="D54" s="2">
-        <v>7270</v>
+        <v>6511</v>
       </c>
       <c r="E54" s="2">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="F54" s="2">
-        <v>7658</v>
+        <v>6827</v>
       </c>
       <c r="G54" s="2">
-        <v>10308</v>
+        <v>10191</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>

--- a/data/adicionales.xlsx
+++ b/data/adicionales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/08 Agosto/Dasboatdde julio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/09 Septiembre/Dasboatdde agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="8_{12694562-3CF4-40B0-8A8E-F17B899F2747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0542C57A-C264-453C-9EDB-6B58B3DF84E2}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="8_{12694562-3CF4-40B0-8A8E-F17B899F2747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D608D6-4E32-4738-B4AC-CC1A3786CE55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E44F7BE-EA21-4B2C-8EEA-8FB69F4EDA70}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>Sucursal</t>
   </si>
@@ -152,37 +152,43 @@
     <t>Motorola Moto G77 256Gb 5G</t>
   </si>
   <si>
-    <t>Honor X7d 256gb</t>
-  </si>
-  <si>
     <t>Vivo Y21d  256/4gb 4g</t>
   </si>
   <si>
-    <t>Conectados 26.1 V65.9lo_mm_ap1</t>
-  </si>
-  <si>
     <t>Conectados 26 E 3.3</t>
   </si>
   <si>
-    <t>Edge Neg 60gb</t>
-  </si>
-  <si>
     <t>NECHI</t>
   </si>
   <si>
     <t>Xiaomi Redmi 15c 256gb</t>
   </si>
   <si>
-    <t>Oppo A6 256Gb 4G</t>
-  </si>
-  <si>
-    <t>Edge 10 Neg 60gb</t>
-  </si>
-  <si>
-    <t>Paquete Power 26.1 V 47.9</t>
-  </si>
-  <si>
     <t>Conectados 26.1v99.9lo_mm_ap1l</t>
+  </si>
+  <si>
+    <t>METRO EST. SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A17 128Gb 4G</t>
+  </si>
+  <si>
+    <t>Oppo A6 256Gb 5G</t>
+  </si>
+  <si>
+    <t>Conectados 26.3 V56.9_ap1</t>
+  </si>
+  <si>
+    <t>Conectados 26.3v99.9_tm_ap1l</t>
+  </si>
+  <si>
+    <t>Paquete Power 26.1 V 46.9</t>
+  </si>
+  <si>
+    <t>Conectados 26.1 V 55.9_ec</t>
   </si>
 </sst>
 </file>
@@ -190,7 +196,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -290,7 +296,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D87759-9E7C-4560-ADF4-54D50CDB6565}">
-  <dimension ref="B1:L23"/>
+  <dimension ref="B1:L25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -673,16 +679,16 @@
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G3">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>32</v>
@@ -691,21 +697,21 @@
         <v>53900</v>
       </c>
       <c r="L3" s="8">
-        <v>652</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>33</v>
@@ -714,21 +720,21 @@
         <v>46900</v>
       </c>
       <c r="L4" s="8">
-        <v>372</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>28</v>
@@ -742,188 +748,188 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K6" s="9">
-        <v>51900</v>
+        <v>33000</v>
       </c>
       <c r="L6" s="8">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K7" s="9">
-        <v>33000</v>
+        <v>51900</v>
       </c>
       <c r="L7" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K8" s="9">
-        <v>29715</v>
+        <v>88600</v>
       </c>
       <c r="L8" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K9" s="9">
-        <v>36330</v>
+        <v>51900</v>
       </c>
       <c r="L9" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K10" s="9">
-        <v>47900</v>
+        <v>66700</v>
       </c>
       <c r="L10" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G11">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K11" s="9">
-        <v>51600</v>
+        <v>46900</v>
       </c>
       <c r="L11" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G12">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K12" s="9">
-        <v>66700</v>
+        <v>53900</v>
       </c>
       <c r="L12" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
@@ -931,7 +937,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -939,23 +945,23 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
@@ -963,15 +969,15 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
@@ -979,16 +985,30 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="5">
-        <v>169</v>
-      </c>
+      <c r="C25" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
